--- a/fuction_ensemble/redes-ensemble-s/Teste03/content/results/metrics_14_4.xlsx
+++ b/fuction_ensemble/redes-ensemble-s/Teste03/content/results/metrics_14_4.xlsx
@@ -513,1376 +513,1376 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>model_14_4_0</t>
+          <t>model_14_4_12</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.9976862149423856</v>
+        <v>0.9999416319380324</v>
       </c>
       <c r="C2" t="n">
-        <v>0.7030214099307701</v>
+        <v>0.703067267837629</v>
       </c>
       <c r="D2" t="n">
-        <v>0.9856370669957872</v>
+        <v>0.9995831105295248</v>
       </c>
       <c r="E2" t="n">
-        <v>0.9976228588802175</v>
+        <v>0.9999441370650002</v>
       </c>
       <c r="F2" t="n">
-        <v>0.993673532627912</v>
+        <v>0.9998333186528691</v>
       </c>
       <c r="G2" t="n">
-        <v>0.001373562760510057</v>
+        <v>3.464980295291472e-05</v>
       </c>
       <c r="H2" t="n">
-        <v>0.1762993198722005</v>
+        <v>0.1762720966377306</v>
       </c>
       <c r="I2" t="n">
-        <v>0.001389973602565844</v>
+        <v>0.0001143488578975125</v>
       </c>
       <c r="J2" t="n">
-        <v>0.0004661693011318452</v>
+        <v>3.174062270878666e-05</v>
       </c>
       <c r="K2" t="n">
-        <v>0.0009280710779230967</v>
+        <v>7.304474030314958e-05</v>
       </c>
       <c r="L2" t="n">
-        <v>0.01327516238434584</v>
+        <v>0.003984067100183668</v>
       </c>
       <c r="M2" t="n">
-        <v>0.03706160763526128</v>
+        <v>0.00588640832366518</v>
       </c>
       <c r="N2" t="n">
-        <v>1.002056697828991</v>
+        <v>1.000051882721749</v>
       </c>
       <c r="O2" t="n">
-        <v>0.03863939700039857</v>
+        <v>0.006137004912548664</v>
       </c>
       <c r="P2" t="n">
-        <v>115.1806947192354</v>
+        <v>122.5404370382582</v>
       </c>
       <c r="Q2" t="n">
-        <v>177.3433617875137</v>
+        <v>184.7031041065364</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>model_14_4_1</t>
+          <t>model_14_4_13</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.9979636946234056</v>
+        <v>0.9999372791217073</v>
       </c>
       <c r="C3" t="n">
-        <v>0.702768475080742</v>
+        <v>0.7030586623994617</v>
       </c>
       <c r="D3" t="n">
-        <v>0.9885399169453012</v>
+        <v>0.9995132216029389</v>
       </c>
       <c r="E3" t="n">
-        <v>0.9980894509157565</v>
+        <v>0.9999373854359209</v>
       </c>
       <c r="F3" t="n">
-        <v>0.9949428985674529</v>
+        <v>0.9998070697944026</v>
       </c>
       <c r="G3" t="n">
-        <v>0.001208838835358521</v>
+        <v>3.723382275542031e-05</v>
       </c>
       <c r="H3" t="n">
-        <v>0.1764494729253937</v>
+        <v>0.1762772051975622</v>
       </c>
       <c r="I3" t="n">
-        <v>0.001109050144881366</v>
+        <v>0.0001335187326503078</v>
       </c>
       <c r="J3" t="n">
-        <v>0.0003746682617906055</v>
+        <v>3.557681411680121e-05</v>
       </c>
       <c r="K3" t="n">
-        <v>0.0007418594456642966</v>
+        <v>8.454777338355451e-05</v>
       </c>
       <c r="L3" t="n">
-        <v>0.01259277949972925</v>
+        <v>0.004097418290189942</v>
       </c>
       <c r="M3" t="n">
-        <v>0.03476835968748772</v>
+        <v>0.006101952372431328</v>
       </c>
       <c r="N3" t="n">
-        <v>1.001810049223639</v>
+        <v>1.000055751891816</v>
       </c>
       <c r="O3" t="n">
-        <v>0.03624852073981061</v>
+        <v>0.006361725117708478</v>
       </c>
       <c r="P3" t="n">
-        <v>115.436190040645</v>
+        <v>122.3965859918287</v>
       </c>
       <c r="Q3" t="n">
-        <v>177.5988571089233</v>
+        <v>184.5592530601069</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>model_14_4_2</t>
+          <t>model_14_4_11</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.9982017653095075</v>
+        <v>0.9999452896515741</v>
       </c>
       <c r="C4" t="n">
-        <v>0.7024868491110943</v>
+        <v>0.7030300008909767</v>
       </c>
       <c r="D4" t="n">
-        <v>0.9909304107795485</v>
+        <v>0.9996483873200546</v>
       </c>
       <c r="E4" t="n">
-        <v>0.9983910748128232</v>
+        <v>0.9999498579876016</v>
       </c>
       <c r="F4" t="n">
-        <v>0.9959330003516024</v>
+        <v>0.9998574554474825</v>
       </c>
       <c r="G4" t="n">
-        <v>0.001067509791970205</v>
+        <v>3.247842618955133e-05</v>
       </c>
       <c r="H4" t="n">
-        <v>0.1766166582665851</v>
+        <v>0.1762942199071116</v>
       </c>
       <c r="I4" t="n">
-        <v>0.0008777099774012552</v>
+        <v>9.644404865445601e-05</v>
       </c>
       <c r="J4" t="n">
-        <v>0.0003155183021478612</v>
+        <v>2.849006586211876e-05</v>
       </c>
       <c r="K4" t="n">
-        <v>0.0005966149077530967</v>
+        <v>6.246727662987542e-05</v>
       </c>
       <c r="L4" t="n">
-        <v>0.01192904588198353</v>
+        <v>0.003865759200165316</v>
       </c>
       <c r="M4" t="n">
-        <v>0.03267276835485792</v>
+        <v>0.005698984663038789</v>
       </c>
       <c r="N4" t="n">
-        <v>1.001598430835993</v>
+        <v>1.000048631420823</v>
       </c>
       <c r="O4" t="n">
-        <v>0.03406371574567867</v>
+        <v>0.005941602238668943</v>
       </c>
       <c r="P4" t="n">
-        <v>115.6848532801955</v>
+        <v>122.6698689971999</v>
       </c>
       <c r="Q4" t="n">
-        <v>177.8475203484738</v>
+        <v>184.8325360654782</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>model_14_4_3</t>
+          <t>model_14_4_14</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.9984050221875577</v>
+        <v>0.9999322834786316</v>
       </c>
       <c r="C5" t="n">
-        <v>0.7021832108540862</v>
+        <v>0.7030122830813823</v>
       </c>
       <c r="D5" t="n">
-        <v>0.9928628155414526</v>
+        <v>0.9994393879303369</v>
       </c>
       <c r="E5" t="n">
-        <v>0.9985550229559065</v>
+        <v>0.9999295183323023</v>
       </c>
       <c r="F5" t="n">
-        <v>0.9966799956087593</v>
+        <v>0.9997788630552212</v>
       </c>
       <c r="G5" t="n">
-        <v>0.0009468477289197036</v>
+        <v>4.019945228569529e-05</v>
       </c>
       <c r="H5" t="n">
-        <v>0.1767969110524349</v>
+        <v>0.1763047379642564</v>
       </c>
       <c r="I5" t="n">
-        <v>0.0006907014041710173</v>
+        <v>0.0001537706141065416</v>
       </c>
       <c r="J5" t="n">
-        <v>0.0002833672486630713</v>
+        <v>4.004680424125872e-05</v>
       </c>
       <c r="K5" t="n">
-        <v>0.0004870332640427804</v>
+        <v>9.690880821901517e-05</v>
       </c>
       <c r="L5" t="n">
-        <v>0.01128342852120384</v>
+        <v>0.004205509577510229</v>
       </c>
       <c r="M5" t="n">
-        <v>0.03077089093477314</v>
+        <v>0.006340303800741356</v>
       </c>
       <c r="N5" t="n">
-        <v>1.001417758055504</v>
+        <v>1.000060192463438</v>
       </c>
       <c r="O5" t="n">
-        <v>0.03208087146639187</v>
+        <v>0.00661022365977714</v>
       </c>
       <c r="P5" t="n">
-        <v>115.9247445416444</v>
+        <v>122.2433143743321</v>
       </c>
       <c r="Q5" t="n">
-        <v>178.0874116099227</v>
+        <v>184.4059814426104</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>model_14_4_4</t>
+          <t>model_14_4_10</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.9985774922569164</v>
+        <v>0.99994824218846</v>
       </c>
       <c r="C6" t="n">
-        <v>0.7018635906134316</v>
+        <v>0.7029382299135032</v>
       </c>
       <c r="D6" t="n">
-        <v>0.9943869783819017</v>
+        <v>0.9997090085856047</v>
       </c>
       <c r="E6" t="n">
-        <v>0.9986045944205044</v>
+        <v>0.9999546810271948</v>
       </c>
       <c r="F6" t="n">
-        <v>0.9972158708256766</v>
+        <v>0.9998795539547984</v>
       </c>
       <c r="G6" t="n">
-        <v>0.0008444620454293592</v>
+        <v>3.072567275119663e-05</v>
       </c>
       <c r="H6" t="n">
-        <v>0.1769866514341628</v>
+        <v>0.1763486991236398</v>
       </c>
       <c r="I6" t="n">
-        <v>0.0005432004645220905</v>
+        <v>7.981620609450315e-05</v>
       </c>
       <c r="J6" t="n">
-        <v>0.0002736460357256673</v>
+        <v>2.574967493858253e-05</v>
       </c>
       <c r="K6" t="n">
-        <v>0.0004084222065684457</v>
+        <v>5.278305127555794e-05</v>
       </c>
       <c r="L6" t="n">
-        <v>0.01065526978020565</v>
+        <v>0.003741708490568207</v>
       </c>
       <c r="M6" t="n">
-        <v>0.02905962913440843</v>
+        <v>0.005543074305040176</v>
       </c>
       <c r="N6" t="n">
-        <v>1.001264451327185</v>
+        <v>1.000046006943591</v>
       </c>
       <c r="O6" t="n">
-        <v>0.03029675770838536</v>
+        <v>0.005779054453951396</v>
       </c>
       <c r="P6" t="n">
-        <v>116.1536215319434</v>
+        <v>122.7808240137253</v>
       </c>
       <c r="Q6" t="n">
-        <v>178.3162886002216</v>
+        <v>184.9434910820036</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>model_14_4_5</t>
+          <t>model_14_4_15</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.9987226970914406</v>
+        <v>0.9999266969234309</v>
       </c>
       <c r="C7" t="n">
-        <v>0.7015326525709824</v>
+        <v>0.702935855434272</v>
       </c>
       <c r="D7" t="n">
-        <v>0.9955476483561456</v>
+        <v>0.9993621537712585</v>
       </c>
       <c r="E7" t="n">
-        <v>0.9985592949824245</v>
+        <v>0.9999205067989259</v>
       </c>
       <c r="F7" t="n">
-        <v>0.9975684171842962</v>
+        <v>0.9997488504585565</v>
       </c>
       <c r="G7" t="n">
-        <v>0.0007582621831335183</v>
+        <v>4.351587277938707e-05</v>
       </c>
       <c r="H7" t="n">
-        <v>0.1771831105519397</v>
+        <v>0.1763501087170836</v>
       </c>
       <c r="I7" t="n">
-        <v>0.0004308765662614352</v>
+        <v>0.0001749552169971348</v>
       </c>
       <c r="J7" t="n">
-        <v>0.0002825294828275775</v>
+        <v>4.516704507588281e-05</v>
       </c>
       <c r="K7" t="n">
-        <v>0.000356704864200496</v>
+        <v>0.0001100612236927564</v>
       </c>
       <c r="L7" t="n">
-        <v>0.01013292203179959</v>
+        <v>0.004323254143352079</v>
       </c>
       <c r="M7" t="n">
-        <v>0.02753656084433055</v>
+        <v>0.00659665618168683</v>
       </c>
       <c r="N7" t="n">
-        <v>1.001135380363164</v>
+        <v>1.000065158290284</v>
       </c>
       <c r="O7" t="n">
-        <v>0.02870884924801286</v>
+        <v>0.006877489492302048</v>
       </c>
       <c r="P7" t="n">
-        <v>116.3689626881769</v>
+        <v>122.0847695898924</v>
       </c>
       <c r="Q7" t="n">
-        <v>178.5316297564551</v>
+        <v>184.2474366581706</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>model_14_4_6</t>
+          <t>model_14_4_16</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.9988438117226832</v>
+        <v>0.9999205382703662</v>
       </c>
       <c r="C8" t="n">
-        <v>0.7011942928511372</v>
+        <v>0.702834775595325</v>
       </c>
       <c r="D8" t="n">
-        <v>0.9963839405822018</v>
+        <v>0.9992816552180158</v>
       </c>
       <c r="E8" t="n">
-        <v>0.9984351392833232</v>
+        <v>0.9999102796814011</v>
       </c>
       <c r="F8" t="n">
-        <v>0.997761292680222</v>
+        <v>0.9997170286737241</v>
       </c>
       <c r="G8" t="n">
-        <v>0.0006863633061482356</v>
+        <v>4.71719152786414e-05</v>
       </c>
       <c r="H8" t="n">
-        <v>0.1773839754980188</v>
+        <v>0.1764101140759041</v>
       </c>
       <c r="I8" t="n">
-        <v>0.0003499443417702238</v>
+        <v>0.0001970352124818177</v>
       </c>
       <c r="J8" t="n">
-        <v>0.0003068770383849451</v>
+        <v>5.097796565769648e-05</v>
       </c>
       <c r="K8" t="n">
-        <v>0.0003284106900775845</v>
+        <v>0.0001240064794102218</v>
       </c>
       <c r="L8" t="n">
-        <v>0.009628211614743176</v>
+        <v>0.004474905324620107</v>
       </c>
       <c r="M8" t="n">
-        <v>0.0261985363359909</v>
+        <v>0.006868181366172663</v>
       </c>
       <c r="N8" t="n">
-        <v>1.001027722913171</v>
+        <v>1.000070632648563</v>
       </c>
       <c r="O8" t="n">
-        <v>0.02731386226626063</v>
+        <v>0.007160574066026061</v>
       </c>
       <c r="P8" t="n">
-        <v>116.5682069392564</v>
+        <v>121.9234237154953</v>
       </c>
       <c r="Q8" t="n">
-        <v>178.7308740075347</v>
+        <v>184.0860907837735</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>model_14_4_7</t>
+          <t>model_14_4_9</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.9989434912039149</v>
+        <v>0.9999504339574088</v>
       </c>
       <c r="C9" t="n">
-        <v>0.7008513314636799</v>
+        <v>0.7027839856645126</v>
       </c>
       <c r="D9" t="n">
-        <v>0.9969300675903749</v>
+        <v>0.9997642094257919</v>
       </c>
       <c r="E9" t="n">
-        <v>0.9982447180968481</v>
+        <v>0.999958749270828</v>
       </c>
       <c r="F9" t="n">
-        <v>0.9978141532201521</v>
+        <v>0.9998994668482721</v>
       </c>
       <c r="G9" t="n">
-        <v>0.0006271892601597443</v>
+        <v>2.942454402367258e-05</v>
       </c>
       <c r="H9" t="n">
-        <v>0.1775875721927739</v>
+        <v>0.1764402651728451</v>
       </c>
       <c r="I9" t="n">
-        <v>0.0002970928716153275</v>
+        <v>6.467513519339519e-05</v>
       </c>
       <c r="J9" t="n">
-        <v>0.0003442195885099829</v>
+        <v>2.34381496625008e-05</v>
       </c>
       <c r="K9" t="n">
-        <v>0.0003206562300626552</v>
+        <v>4.405662712848808e-05</v>
       </c>
       <c r="L9" t="n">
-        <v>0.009140021677567218</v>
+        <v>0.003612798742837015</v>
       </c>
       <c r="M9" t="n">
-        <v>0.02504374692732188</v>
+        <v>0.005424439512398731</v>
       </c>
       <c r="N9" t="n">
-        <v>1.000939118929853</v>
+        <v>1.000044058704526</v>
       </c>
       <c r="O9" t="n">
-        <v>0.02610991108172095</v>
+        <v>0.005655369132579328</v>
       </c>
       <c r="P9" t="n">
-        <v>116.748524425089</v>
+        <v>122.8673628023197</v>
       </c>
       <c r="Q9" t="n">
-        <v>178.9111914933672</v>
+        <v>185.0300298705979</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>model_14_4_8</t>
+          <t>model_14_4_17</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.9990241181919254</v>
+        <v>0.9999138902840704</v>
       </c>
       <c r="C10" t="n">
-        <v>0.7005057014216309</v>
+        <v>0.7027152754631887</v>
       </c>
       <c r="D10" t="n">
-        <v>0.9972167845834778</v>
+        <v>0.9991986773425441</v>
       </c>
       <c r="E10" t="n">
-        <v>0.9979984488928043</v>
+        <v>0.9998989126438681</v>
       </c>
       <c r="F10" t="n">
-        <v>0.9977441189511916</v>
+        <v>0.9996836909934684</v>
       </c>
       <c r="G10" t="n">
-        <v>0.0005793255971721942</v>
+        <v>5.111844712187541e-05</v>
       </c>
       <c r="H10" t="n">
-        <v>0.1777927531161746</v>
+        <v>0.1764810545164772</v>
       </c>
       <c r="I10" t="n">
-        <v>0.0002693458194148417</v>
+        <v>0.0002197952627180081</v>
       </c>
       <c r="J10" t="n">
-        <v>0.0003925142151032448</v>
+        <v>5.743657456630967e-05</v>
       </c>
       <c r="K10" t="n">
-        <v>0.0003309300172590433</v>
+        <v>0.0001386160457384128</v>
       </c>
       <c r="L10" t="n">
-        <v>0.008666908748526683</v>
+        <v>0.004622321337089573</v>
       </c>
       <c r="M10" t="n">
-        <v>0.02406918355848811</v>
+        <v>0.007149716576331918</v>
       </c>
       <c r="N10" t="n">
-        <v>1.000867450496066</v>
+        <v>1.000076541969715</v>
       </c>
       <c r="O10" t="n">
-        <v>0.02509385853265162</v>
+        <v>0.007454094812940023</v>
       </c>
       <c r="P10" t="n">
-        <v>116.907291788908</v>
+        <v>121.762730250943</v>
       </c>
       <c r="Q10" t="n">
-        <v>179.0699588571862</v>
+        <v>183.9253973192212</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>model_14_4_9</t>
+          <t>model_14_4_18</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.9990877020245256</v>
+        <v>0.9999067453197453</v>
       </c>
       <c r="C11" t="n">
-        <v>0.7001588727831315</v>
+        <v>0.7025802974768577</v>
       </c>
       <c r="D11" t="n">
-        <v>0.9972706678620495</v>
+        <v>0.9991130876660705</v>
       </c>
       <c r="E11" t="n">
-        <v>0.997704514501777</v>
+        <v>0.9998863434185065</v>
       </c>
       <c r="F11" t="n">
-        <v>0.9975654343733119</v>
+        <v>0.9996487574236573</v>
       </c>
       <c r="G11" t="n">
-        <v>0.000541579487462176</v>
+        <v>5.536000659163698e-05</v>
       </c>
       <c r="H11" t="n">
-        <v>0.1779986455782049</v>
+        <v>0.1765611832799087</v>
       </c>
       <c r="I11" t="n">
-        <v>0.0002641312622758217</v>
+        <v>0.0002432717053861401</v>
       </c>
       <c r="J11" t="n">
-        <v>0.0004501562240288059</v>
+        <v>6.457825160042621e-05</v>
       </c>
       <c r="K11" t="n">
-        <v>0.0003571424323475469</v>
+        <v>0.0001539249784932831</v>
       </c>
       <c r="L11" t="n">
-        <v>0.008306829225255942</v>
+        <v>0.004766748010560383</v>
       </c>
       <c r="M11" t="n">
-        <v>0.02327186042116479</v>
+        <v>0.007440430538056046</v>
       </c>
       <c r="N11" t="n">
-        <v>1.000810931533755</v>
+        <v>1.000082893049115</v>
       </c>
       <c r="O11" t="n">
-        <v>0.02426259169868602</v>
+        <v>0.007757185069875609</v>
       </c>
       <c r="P11" t="n">
-        <v>117.0420414220909</v>
+        <v>121.6033062551726</v>
       </c>
       <c r="Q11" t="n">
-        <v>179.2047084903691</v>
+        <v>183.7659733234508</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>model_14_4_10</t>
+          <t>model_14_4_8</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.9991360426348872</v>
+        <v>0.9999518757589686</v>
       </c>
       <c r="C12" t="n">
-        <v>0.6998122210299333</v>
+        <v>0.7025579398142858</v>
       </c>
       <c r="D12" t="n">
-        <v>0.9971160273403283</v>
+        <v>0.999814215347554</v>
       </c>
       <c r="E12" t="n">
-        <v>0.9973693482254771</v>
+        <v>0.9999621854043473</v>
       </c>
       <c r="F12" t="n">
-        <v>0.9972903912909498</v>
+        <v>0.9999173438518288</v>
       </c>
       <c r="G12" t="n">
-        <v>0.0005128824129458414</v>
+        <v>2.856862833522426e-05</v>
       </c>
       <c r="H12" t="n">
-        <v>0.1782044330334794</v>
+        <v>0.1765744557542121</v>
       </c>
       <c r="I12" t="n">
-        <v>0.0002790966069596947</v>
+        <v>5.095898152062013e-05</v>
       </c>
       <c r="J12" t="n">
-        <v>0.0005158840125414203</v>
+        <v>2.148578146671828e-05</v>
       </c>
       <c r="K12" t="n">
-        <v>0.0003974903097505575</v>
+        <v>3.622239069667245e-05</v>
       </c>
       <c r="L12" t="n">
-        <v>0.00820777315481225</v>
+        <v>0.003477271572266665</v>
       </c>
       <c r="M12" t="n">
-        <v>0.02264690735941315</v>
+        <v>0.005344962893718184</v>
       </c>
       <c r="N12" t="n">
-        <v>1.000767962102322</v>
+        <v>1.000042777103139</v>
       </c>
       <c r="O12" t="n">
-        <v>0.02361103309126443</v>
+        <v>0.005572509029702269</v>
       </c>
       <c r="P12" t="n">
-        <v>117.1509279071954</v>
+        <v>122.9264027070837</v>
       </c>
       <c r="Q12" t="n">
-        <v>179.3135949754736</v>
+        <v>185.0890697753619</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>model_14_4_11</t>
+          <t>model_14_4_19</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.9991707353841811</v>
+        <v>0.9998991938794591</v>
       </c>
       <c r="C13" t="n">
-        <v>0.6994665263884758</v>
+        <v>0.70243433090929</v>
       </c>
       <c r="D13" t="n">
-        <v>0.9967743058096707</v>
+        <v>0.9990256986389254</v>
       </c>
       <c r="E13" t="n">
-        <v>0.9969976305317522</v>
+        <v>0.9998726915993086</v>
       </c>
       <c r="F13" t="n">
-        <v>0.99692920903843</v>
+        <v>0.9996125590040941</v>
       </c>
       <c r="G13" t="n">
-        <v>0.0004922872983162407</v>
+        <v>5.984286775073782e-05</v>
       </c>
       <c r="H13" t="n">
-        <v>0.1784096523058795</v>
+        <v>0.1766478353398442</v>
       </c>
       <c r="I13" t="n">
-        <v>0.0003121667261966976</v>
+        <v>0.0002672416930076397</v>
       </c>
       <c r="J13" t="n">
-        <v>0.0005887797174114533</v>
+        <v>7.233504494561932e-05</v>
       </c>
       <c r="K13" t="n">
-        <v>0.0004504745081519615</v>
+        <v>0.0001697882061542868</v>
       </c>
       <c r="L13" t="n">
-        <v>0.008303782736753963</v>
+        <v>0.004907084540320167</v>
       </c>
       <c r="M13" t="n">
-        <v>0.02218754827186277</v>
+        <v>0.007735817199930323</v>
       </c>
       <c r="N13" t="n">
-        <v>1.00073712410295</v>
+        <v>1.000089605440481</v>
       </c>
       <c r="O13" t="n">
-        <v>0.02313211813635264</v>
+        <v>0.008065146953480561</v>
       </c>
       <c r="P13" t="n">
-        <v>117.2328961444625</v>
+        <v>121.4475766036087</v>
       </c>
       <c r="Q13" t="n">
-        <v>179.3955632127407</v>
+        <v>183.6102436718869</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>model_14_4_12</t>
+          <t>model_14_4_20</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.9991931282744343</v>
+        <v>0.9998913106519516</v>
       </c>
       <c r="C14" t="n">
-        <v>0.6991210791784488</v>
+        <v>0.7022813940509378</v>
       </c>
       <c r="D14" t="n">
-        <v>0.9962644036651531</v>
+        <v>0.9989371011823417</v>
       </c>
       <c r="E14" t="n">
-        <v>0.9965935428236089</v>
+        <v>0.9998580859670329</v>
       </c>
       <c r="F14" t="n">
-        <v>0.9964909341029415</v>
+        <v>0.9995753625204366</v>
       </c>
       <c r="G14" t="n">
-        <v>0.0004789939113394887</v>
+        <v>6.452269213688802e-05</v>
       </c>
       <c r="H14" t="n">
-        <v>0.178614724692294</v>
+        <v>0.1767386252654904</v>
       </c>
       <c r="I14" t="n">
-        <v>0.0003615125332517989</v>
+        <v>0.0002915431414501171</v>
       </c>
       <c r="J14" t="n">
-        <v>0.0006680233445287084</v>
+        <v>8.063378298160377e-05</v>
       </c>
       <c r="K14" t="n">
-        <v>0.0005147679388902537</v>
+        <v>0.0001860888152849324</v>
       </c>
       <c r="L14" t="n">
-        <v>0.008393806269289121</v>
+        <v>0.005042718578773983</v>
       </c>
       <c r="M14" t="n">
-        <v>0.02188592952879746</v>
+        <v>0.008032601828603733</v>
       </c>
       <c r="N14" t="n">
-        <v>1.000717219311614</v>
+        <v>1.000096612753821</v>
       </c>
       <c r="O14" t="n">
-        <v>0.02281765885895817</v>
+        <v>0.008374566318225472</v>
       </c>
       <c r="P14" t="n">
-        <v>117.2876453436504</v>
+        <v>121.2969871599191</v>
       </c>
       <c r="Q14" t="n">
-        <v>179.4503124119286</v>
+        <v>183.4596542281973</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
         <is>
-          <t>model_14_4_13</t>
+          <t>model_14_4_7</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.9992044406052012</v>
+        <v>0.9999525145422311</v>
       </c>
       <c r="C15" t="n">
-        <v>0.6987770288749962</v>
+        <v>0.7022517074660852</v>
       </c>
       <c r="D15" t="n">
-        <v>0.9956034908729197</v>
+        <v>0.9998585557372394</v>
       </c>
       <c r="E15" t="n">
-        <v>0.9961600546957319</v>
+        <v>0.9999650857649678</v>
       </c>
       <c r="F15" t="n">
-        <v>0.995983188539587</v>
+        <v>0.999933100559123</v>
       </c>
       <c r="G15" t="n">
-        <v>0.0004722784231289843</v>
+        <v>2.818941899660226e-05</v>
       </c>
       <c r="H15" t="n">
-        <v>0.1788189678146227</v>
+        <v>0.1767562485046525</v>
       </c>
       <c r="I15" t="n">
-        <v>0.000425472403741564</v>
+        <v>3.879682997126483e-05</v>
       </c>
       <c r="J15" t="n">
-        <v>0.0007530325414752848</v>
+        <v>1.983783274772941e-05</v>
       </c>
       <c r="K15" t="n">
-        <v>0.0005892524726084244</v>
+        <v>2.931733135949712e-05</v>
       </c>
       <c r="L15" t="n">
-        <v>0.008478238905189107</v>
+        <v>0.003335110009139642</v>
       </c>
       <c r="M15" t="n">
-        <v>0.0217319677693711</v>
+        <v>0.005309370866364701</v>
       </c>
       <c r="N15" t="n">
-        <v>1.000707163906488</v>
+        <v>1.000042209295795</v>
       </c>
       <c r="O15" t="n">
-        <v>0.02265714262868825</v>
+        <v>0.005535401776058695</v>
       </c>
       <c r="P15" t="n">
-        <v>117.3158837335574</v>
+        <v>122.9531277266332</v>
       </c>
       <c r="Q15" t="n">
-        <v>179.4785508018356</v>
+        <v>185.1157947949115</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>model_14_4_14</t>
+          <t>model_14_4_21</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.9992057253643613</v>
+        <v>0.999883159980189</v>
       </c>
       <c r="C16" t="n">
-        <v>0.6984334085617614</v>
+        <v>0.7021238725504837</v>
       </c>
       <c r="D16" t="n">
-        <v>0.9948064080560132</v>
+        <v>0.9988478172569704</v>
       </c>
       <c r="E16" t="n">
-        <v>0.9956986703604485</v>
+        <v>0.999842645766465</v>
       </c>
       <c r="F16" t="n">
-        <v>0.9954118816833134</v>
+        <v>0.9995374121433759</v>
       </c>
       <c r="G16" t="n">
-        <v>0.000471515734592852</v>
+        <v>6.936128298585723e-05</v>
       </c>
       <c r="H16" t="n">
-        <v>0.1790229556761836</v>
+        <v>0.1768321368327344</v>
       </c>
       <c r="I16" t="n">
-        <v>0.0005026101355846306</v>
+        <v>0.0003160328818198756</v>
       </c>
       <c r="J16" t="n">
-        <v>0.00084351232466624</v>
+        <v>8.94067123090094e-05</v>
       </c>
       <c r="K16" t="n">
-        <v>0.0006730612301254352</v>
+        <v>0.0002027198030020167</v>
       </c>
       <c r="L16" t="n">
-        <v>0.008557850725479571</v>
+        <v>0.005173564560448742</v>
       </c>
       <c r="M16" t="n">
-        <v>0.0217144130612101</v>
+        <v>0.008328342151104097</v>
       </c>
       <c r="N16" t="n">
-        <v>1.000706021898345</v>
+        <v>1.000103857795388</v>
       </c>
       <c r="O16" t="n">
-        <v>0.02263884058025758</v>
+        <v>0.008682896918521543</v>
       </c>
       <c r="P16" t="n">
-        <v>117.3191161701895</v>
+        <v>121.1523634563475</v>
       </c>
       <c r="Q16" t="n">
-        <v>179.4817832384678</v>
+        <v>183.3150305246258</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
         <is>
-          <t>model_14_4_15</t>
+          <t>model_14_4_22</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.9991979532146587</v>
+        <v>0.9998747414601629</v>
       </c>
       <c r="C17" t="n">
-        <v>0.698090355211286</v>
+        <v>0.7019624996288079</v>
       </c>
       <c r="D17" t="n">
-        <v>0.9938890897172821</v>
+        <v>0.9987577251855001</v>
       </c>
       <c r="E17" t="n">
-        <v>0.9952117025292875</v>
+        <v>0.9998263581517625</v>
       </c>
       <c r="F17" t="n">
-        <v>0.9947838064934551</v>
+        <v>0.9994986581803468</v>
       </c>
       <c r="G17" t="n">
-        <v>0.0004761296183957388</v>
+        <v>7.435888013453229e-05</v>
       </c>
       <c r="H17" t="n">
-        <v>0.1792266069641588</v>
+        <v>0.1769279347699885</v>
       </c>
       <c r="I17" t="n">
-        <v>0.0005913836664234797</v>
+        <v>0.0003407442890580911</v>
       </c>
       <c r="J17" t="n">
-        <v>0.0009390091597665476</v>
+        <v>9.866113177514942e-05</v>
       </c>
       <c r="K17" t="n">
-        <v>0.0007651977075915613</v>
+        <v>0.000219702946070583</v>
       </c>
       <c r="L17" t="n">
-        <v>0.008632571412555287</v>
+        <v>0.00530046274979144</v>
       </c>
       <c r="M17" t="n">
-        <v>0.0218203945517889</v>
+        <v>0.008623159521575156</v>
       </c>
       <c r="N17" t="n">
-        <v>1.000712930475859</v>
+        <v>1.0001113409243</v>
       </c>
       <c r="O17" t="n">
-        <v>0.02274933392230225</v>
+        <v>0.008990265274809645</v>
       </c>
       <c r="P17" t="n">
-        <v>117.2996408664955</v>
+        <v>121.0132149105529</v>
       </c>
       <c r="Q17" t="n">
-        <v>179.4623079347737</v>
+        <v>183.1758819788311</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="inlineStr">
         <is>
-          <t>model_14_4_16</t>
+          <t>model_14_4_6</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0.9991819853692124</v>
+        <v>0.999952291231153</v>
       </c>
       <c r="C18" t="n">
-        <v>0.6977473616223724</v>
+        <v>0.7018584487451007</v>
       </c>
       <c r="D18" t="n">
-        <v>0.9928633158867587</v>
+        <v>0.999896842071515</v>
       </c>
       <c r="E18" t="n">
-        <v>0.9946999718185591</v>
+        <v>0.9999674399763084</v>
       </c>
       <c r="F18" t="n">
-        <v>0.994103423561578</v>
+        <v>0.9999466090036612</v>
       </c>
       <c r="G18" t="n">
-        <v>0.0004856088212276036</v>
+        <v>2.832198609903916e-05</v>
       </c>
       <c r="H18" t="n">
-        <v>0.1794302227750895</v>
+        <v>0.1769897038693212</v>
       </c>
       <c r="I18" t="n">
-        <v>0.0006906529832275091</v>
+        <v>2.829524883871857e-05</v>
       </c>
       <c r="J18" t="n">
-        <v>0.001039362119800225</v>
+        <v>1.850019923563631e-05</v>
       </c>
       <c r="K18" t="n">
-        <v>0.0008650075515138672</v>
+        <v>2.339752785316194e-05</v>
       </c>
       <c r="L18" t="n">
-        <v>0.008703111312820399</v>
+        <v>0.003205187756280552</v>
       </c>
       <c r="M18" t="n">
-        <v>0.02203653378432288</v>
+        <v>0.005321840480420205</v>
       </c>
       <c r="N18" t="n">
-        <v>1.000727124116256</v>
+        <v>1.000042407794531</v>
       </c>
       <c r="O18" t="n">
-        <v>0.02297467464943509</v>
+        <v>0.005548402247400201</v>
       </c>
       <c r="P18" t="n">
-        <v>117.2602143055175</v>
+        <v>122.943744321964</v>
       </c>
       <c r="Q18" t="n">
-        <v>179.4228813737958</v>
+        <v>185.1064113902422</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>model_14_4_17</t>
+          <t>model_14_4_23</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.9991585180968455</v>
+        <v>0.9998661510973336</v>
       </c>
       <c r="C19" t="n">
-        <v>0.6974044022487034</v>
+        <v>0.7018001388514012</v>
       </c>
       <c r="D19" t="n">
-        <v>0.9917405150277626</v>
+        <v>0.998667600744395</v>
       </c>
       <c r="E19" t="n">
-        <v>0.9941639794937641</v>
+        <v>0.9998094347033381</v>
       </c>
       <c r="F19" t="n">
-        <v>0.9933748111146834</v>
+        <v>0.99945948401691</v>
       </c>
       <c r="G19" t="n">
-        <v>0.0004995400078380078</v>
+        <v>7.945849059435744e-05</v>
       </c>
       <c r="H19" t="n">
-        <v>0.179633818274373</v>
+        <v>0.1770243191410774</v>
       </c>
       <c r="I19" t="n">
-        <v>0.0007993120958534021</v>
+        <v>0.0003654645749825087</v>
       </c>
       <c r="J19" t="n">
-        <v>0.001144472904087437</v>
+        <v>0.0001082768240292808</v>
       </c>
       <c r="K19" t="n">
-        <v>0.0009718924999704193</v>
+        <v>0.0002368702334970446</v>
       </c>
       <c r="L19" t="n">
-        <v>0.008769740825795369</v>
+        <v>0.005422710177821848</v>
       </c>
       <c r="M19" t="n">
-        <v>0.02235039167079646</v>
+        <v>0.00891394921425725</v>
       </c>
       <c r="N19" t="n">
-        <v>1.000747983913915</v>
+        <v>1.00011897680237</v>
       </c>
       <c r="O19" t="n">
-        <v>0.02330189411591124</v>
+        <v>0.009293434486726862</v>
       </c>
       <c r="P19" t="n">
-        <v>117.2036457346227</v>
+        <v>120.8805516071007</v>
       </c>
       <c r="Q19" t="n">
-        <v>179.366312802901</v>
+        <v>183.043218675379</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="inlineStr">
         <is>
-          <t>model_14_4_18</t>
+          <t>model_14_4_24</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.999128335070636</v>
+        <v>0.9998574479895009</v>
       </c>
       <c r="C20" t="n">
-        <v>0.6970617813136472</v>
+        <v>0.701638153121663</v>
       </c>
       <c r="D20" t="n">
-        <v>0.9905341783330822</v>
+        <v>0.9985778763729573</v>
       </c>
       <c r="E20" t="n">
-        <v>0.9936055797771959</v>
+        <v>0.9997920010783382</v>
       </c>
       <c r="F20" t="n">
-        <v>0.9926036673847066</v>
+        <v>0.9994201029024413</v>
       </c>
       <c r="G20" t="n">
-        <v>0.0005174579560348111</v>
+        <v>8.46250313584363e-05</v>
       </c>
       <c r="H20" t="n">
-        <v>0.1798372128618761</v>
+        <v>0.1771204808676692</v>
       </c>
       <c r="I20" t="n">
-        <v>0.000916055393404151</v>
+        <v>0.0003900751255626724</v>
       </c>
       <c r="J20" t="n">
-        <v>0.001253977890332704</v>
+        <v>0.0001181823922485175</v>
       </c>
       <c r="K20" t="n">
-        <v>0.001085016641868427</v>
+        <v>0.0002541282130414098</v>
       </c>
       <c r="L20" t="n">
-        <v>0.008832122924146686</v>
+        <v>0.005540148008645194</v>
       </c>
       <c r="M20" t="n">
-        <v>0.02274770221439544</v>
+        <v>0.00919918645090077</v>
       </c>
       <c r="N20" t="n">
-        <v>1.000774813270546</v>
+        <v>1.000126712898221</v>
       </c>
       <c r="O20" t="n">
-        <v>0.02371611899189743</v>
+        <v>0.009590814863056775</v>
       </c>
       <c r="P20" t="n">
-        <v>117.1331645610049</v>
+        <v>120.7545609123486</v>
       </c>
       <c r="Q20" t="n">
-        <v>179.2958316292831</v>
+        <v>182.9172279806269</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="inlineStr">
         <is>
-          <t>model_14_4_19</t>
+          <t>model_14_4_5</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.999091986222058</v>
+        <v>0.9999511190626574</v>
       </c>
       <c r="C21" t="n">
-        <v>0.696718446827882</v>
+        <v>0.7013744206297621</v>
       </c>
       <c r="D21" t="n">
-        <v>0.9892524651809095</v>
+        <v>0.9999284816772217</v>
       </c>
       <c r="E21" t="n">
-        <v>0.9930242265508608</v>
+        <v>0.9999692252500906</v>
       </c>
       <c r="F21" t="n">
-        <v>0.9917922988657499</v>
+        <v>0.9999576680999441</v>
       </c>
       <c r="G21" t="n">
-        <v>0.0005390362027392191</v>
+        <v>2.901783595311233e-05</v>
       </c>
       <c r="H21" t="n">
-        <v>0.1800410310439039</v>
+        <v>0.1772770438675121</v>
       </c>
       <c r="I21" t="n">
-        <v>0.001040093251622872</v>
+        <v>1.961680279217989e-05</v>
       </c>
       <c r="J21" t="n">
-        <v>0.001367984175014768</v>
+        <v>1.748582894605407e-05</v>
       </c>
       <c r="K21" t="n">
-        <v>0.001204041622429182</v>
+        <v>1.855110184397647e-05</v>
       </c>
       <c r="L21" t="n">
-        <v>0.008891267353118551</v>
+        <v>0.003097832293934158</v>
       </c>
       <c r="M21" t="n">
-        <v>0.02321715320058037</v>
+        <v>0.005386820579257521</v>
       </c>
       <c r="N21" t="n">
-        <v>1.000807123358171</v>
+        <v>1.000043449722082</v>
       </c>
       <c r="O21" t="n">
-        <v>0.02420555547846176</v>
+        <v>0.00561614868357237</v>
       </c>
       <c r="P21" t="n">
-        <v>117.0514556456376</v>
+        <v>122.8951997683341</v>
       </c>
       <c r="Q21" t="n">
-        <v>179.2141227139158</v>
+        <v>185.0578668366124</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="inlineStr">
         <is>
-          <t>model_14_4_20</t>
+          <t>model_14_4_4</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.9990500449880834</v>
+        <v>0.9999489048444756</v>
       </c>
       <c r="C22" t="n">
-        <v>0.6963753074816331</v>
+        <v>0.7007962133615895</v>
       </c>
       <c r="D22" t="n">
-        <v>0.9879049295820787</v>
+        <v>0.9999530770707901</v>
       </c>
       <c r="E22" t="n">
-        <v>0.9924209054953992</v>
+        <v>0.9999702635114697</v>
       </c>
       <c r="F22" t="n">
-        <v>0.9909445752511157</v>
+        <v>0.9999660383963848</v>
       </c>
       <c r="G22" t="n">
-        <v>0.0005639343309935039</v>
+        <v>3.033229151503373e-05</v>
       </c>
       <c r="H22" t="n">
-        <v>0.1802447333826851</v>
+        <v>0.1776202926791528</v>
       </c>
       <c r="I22" t="n">
-        <v>0.001170501080604819</v>
+        <v>1.287051783354062e-05</v>
       </c>
       <c r="J22" t="n">
-        <v>0.001486298461214305</v>
+        <v>1.689590178402005e-05</v>
       </c>
       <c r="K22" t="n">
-        <v>0.001328399770909562</v>
+        <v>1.488298816306898e-05</v>
       </c>
       <c r="L22" t="n">
-        <v>0.008946985173964344</v>
+        <v>0.002989791648618894</v>
       </c>
       <c r="M22" t="n">
-        <v>0.02374730155182908</v>
+        <v>0.005507475965906137</v>
       </c>
       <c r="N22" t="n">
-        <v>1.000844404455037</v>
+        <v>1.000045417916022</v>
       </c>
       <c r="O22" t="n">
-        <v>0.02475827334258151</v>
+        <v>0.0057419406198217</v>
       </c>
       <c r="P22" t="n">
-        <v>116.9611454953078</v>
+        <v>122.8065953727272</v>
       </c>
       <c r="Q22" t="n">
-        <v>179.1238125635861</v>
+        <v>184.9692624410054</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="1" t="inlineStr">
         <is>
-          <t>model_14_4_21</t>
+          <t>model_14_4_3</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.9990030811872693</v>
+        <v>0.999945515115914</v>
       </c>
       <c r="C23" t="n">
-        <v>0.6960313435997916</v>
+        <v>0.7001255491900329</v>
       </c>
       <c r="D23" t="n">
-        <v>0.9865018213730138</v>
+        <v>0.9999698964066467</v>
       </c>
       <c r="E23" t="n">
-        <v>0.9917961178278535</v>
+        <v>0.9999703504260973</v>
       </c>
       <c r="F23" t="n">
-        <v>0.9900641529485897</v>
+        <v>0.9999713573417245</v>
       </c>
       <c r="G23" t="n">
-        <v>0.0005918140718872798</v>
+        <v>3.234458081789186e-05</v>
       </c>
       <c r="H23" t="n">
-        <v>0.1804489252014123</v>
+        <v>0.1780184279025725</v>
       </c>
       <c r="I23" t="n">
-        <v>0.001306286951886934</v>
+        <v>8.257132315278236e-06</v>
       </c>
       <c r="J23" t="n">
-        <v>0.001608822457754412</v>
+        <v>1.684651797697741e-05</v>
       </c>
       <c r="K23" t="n">
-        <v>0.001457554704820673</v>
+        <v>1.255206759089987e-05</v>
       </c>
       <c r="L23" t="n">
-        <v>0.008999455062364081</v>
+        <v>0.002956798513119631</v>
       </c>
       <c r="M23" t="n">
-        <v>0.02432722902196795</v>
+        <v>0.005687229625915579</v>
       </c>
       <c r="N23" t="n">
-        <v>1.000886150055761</v>
+        <v>1.000048431008076</v>
       </c>
       <c r="O23" t="n">
-        <v>0.02536288952573956</v>
+        <v>0.005929346765279117</v>
       </c>
       <c r="P23" t="n">
-        <v>116.8646360803357</v>
+        <v>122.6781281365424</v>
       </c>
       <c r="Q23" t="n">
-        <v>179.0273031486139</v>
+        <v>184.8407952048207</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>model_14_4_22</t>
+          <t>model_14_4_2</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.9989515910115906</v>
+        <v>0.9999408073032092</v>
       </c>
       <c r="C24" t="n">
-        <v>0.6956870468898492</v>
+        <v>0.6993617869076301</v>
       </c>
       <c r="D24" t="n">
-        <v>0.9850515790827398</v>
+        <v>0.9999782955228099</v>
       </c>
       <c r="E24" t="n">
-        <v>0.9911506317197672</v>
+        <v>0.9999692009955827</v>
       </c>
       <c r="F24" t="n">
-        <v>0.9891543486669179</v>
+        <v>0.999973241226519</v>
       </c>
       <c r="G24" t="n">
-        <v>0.0006223808644299466</v>
+        <v>3.513934180635936e-05</v>
       </c>
       <c r="H24" t="n">
-        <v>0.1806533146012775</v>
+        <v>0.1784718301862195</v>
       </c>
       <c r="I24" t="n">
-        <v>0.001446634226375665</v>
+        <v>5.953333805998343e-06</v>
       </c>
       <c r="J24" t="n">
-        <v>0.00173540552234101</v>
+        <v>1.749961005483731e-05</v>
       </c>
       <c r="K24" t="n">
-        <v>0.001591019874358337</v>
+        <v>1.172649305632817e-05</v>
       </c>
       <c r="L24" t="n">
-        <v>0.009048810335369474</v>
+        <v>0.003157637914868071</v>
       </c>
       <c r="M24" t="n">
-        <v>0.02494756229433943</v>
+        <v>0.005927844617258398</v>
       </c>
       <c r="N24" t="n">
-        <v>1.000931919100808</v>
+        <v>1.000052615730481</v>
       </c>
       <c r="O24" t="n">
-        <v>0.02600963166978279</v>
+        <v>0.006180205234945097</v>
       </c>
       <c r="P24" t="n">
-        <v>116.7639166607664</v>
+        <v>122.5123784119818</v>
       </c>
       <c r="Q24" t="n">
-        <v>178.9265837290447</v>
+        <v>184.67504548026</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
         <is>
-          <t>model_14_4_23</t>
+          <t>model_14_4_1</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.9988959891318857</v>
+        <v>0.9999346235632527</v>
       </c>
       <c r="C25" t="n">
-        <v>0.6953423052935026</v>
+        <v>0.6985135527460689</v>
       </c>
       <c r="D25" t="n">
-        <v>0.983561976556669</v>
+        <v>0.9999774095103474</v>
       </c>
       <c r="E25" t="n">
-        <v>0.9904843595557846</v>
+        <v>0.9999665515418219</v>
       </c>
       <c r="F25" t="n">
-        <v>0.9882176572108637</v>
+        <v>0.9999712468927704</v>
       </c>
       <c r="G25" t="n">
-        <v>0.0006553885420989218</v>
+        <v>3.881027696822842e-05</v>
       </c>
       <c r="H25" t="n">
-        <v>0.1808579681049304</v>
+        <v>0.1789753786263301</v>
       </c>
       <c r="I25" t="n">
-        <v>0.001590790589769297</v>
+        <v>6.196358685124343e-06</v>
       </c>
       <c r="J25" t="n">
-        <v>0.001866064836784992</v>
+        <v>1.900499662655853e-05</v>
       </c>
       <c r="K25" t="n">
-        <v>0.001728429300215318</v>
+        <v>1.260046961849829e-05</v>
       </c>
       <c r="L25" t="n">
-        <v>0.009095107887020943</v>
+        <v>0.003365389749697084</v>
       </c>
       <c r="M25" t="n">
-        <v>0.02560055745680007</v>
+        <v>0.006229789480249588</v>
       </c>
       <c r="N25" t="n">
-        <v>1.000981342993879</v>
+        <v>1.00005811238822</v>
       </c>
       <c r="O25" t="n">
-        <v>0.02669042618819572</v>
+        <v>0.006495004515865855</v>
       </c>
       <c r="P25" t="n">
-        <v>116.6605646083098</v>
+        <v>122.3136509521837</v>
       </c>
       <c r="Q25" t="n">
-        <v>178.8232316765881</v>
+        <v>184.4763180204619</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="1" t="inlineStr">
         <is>
-          <t>model_14_4_24</t>
+          <t>model_14_4_0</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.9988367325313089</v>
+        <v>0.9999268150723596</v>
       </c>
       <c r="C26" t="n">
-        <v>0.6949974251099498</v>
+        <v>0.6975916780646101</v>
       </c>
       <c r="D26" t="n">
-        <v>0.9820408439100371</v>
+        <v>0.9999664570548574</v>
       </c>
       <c r="E26" t="n">
-        <v>0.9897986026876843</v>
+        <v>0.9999621914661557</v>
       </c>
       <c r="F26" t="n">
-        <v>0.9872575645679863</v>
+        <v>0.9999649918217158</v>
       </c>
       <c r="G26" t="n">
-        <v>0.0006905658199531684</v>
+        <v>4.344573447160122e-05</v>
       </c>
       <c r="H26" t="n">
-        <v>0.1810627038799356</v>
+        <v>0.1795226432601567</v>
       </c>
       <c r="I26" t="n">
-        <v>0.001737998282251</v>
+        <v>9.200514139154821e-06</v>
       </c>
       <c r="J26" t="n">
-        <v>0.002000545199472913</v>
+        <v>2.148233722284139e-05</v>
       </c>
       <c r="K26" t="n">
-        <v>0.001869271599965804</v>
+        <v>1.534162841413973e-05</v>
       </c>
       <c r="L26" t="n">
-        <v>0.00913840069637405</v>
+        <v>0.003624292810808743</v>
       </c>
       <c r="M26" t="n">
-        <v>0.02627861906480568</v>
+        <v>0.006591337836251546</v>
       </c>
       <c r="N26" t="n">
-        <v>1.001034015527726</v>
+        <v>1.000065053269014</v>
       </c>
       <c r="O26" t="n">
-        <v>0.02739735428263515</v>
+        <v>0.006871944733891092</v>
       </c>
       <c r="P26" t="n">
-        <v>116.5559985349907</v>
+        <v>122.0879957640725</v>
       </c>
       <c r="Q26" t="n">
-        <v>178.7186656032689</v>
+        <v>184.2506628323507</v>
       </c>
     </row>
   </sheetData>
